--- a/islami-assistant-web/public/data/هواتف عمان .xlsx
+++ b/islami-assistant-web/public/data/هواتف عمان .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BLACK-DIAMOND\Desktop\islami Assistant\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BLACK-DIAMOND\Desktop\islami Assistant\islami-assistant-web\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4F72CBB-1ED6-4B8C-A039-ECF62D6A497D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE3D02E-1665-4461-9DAA-6F0EED547742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="84">
   <si>
     <t>الموقع</t>
   </si>
@@ -45,9 +45,6 @@
     <t>عمّان/ شارع مكة /داخل مجمع مكة مول/ الطابق الأرضي</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5004</t>
-  </si>
-  <si>
     <t>709 الرمز البريدي 11821</t>
   </si>
   <si>
@@ -57,9 +54,6 @@
     <t>محافظة العاصمة - منطقة مرج الحمام -شارع الأميرة تغريد - دوار الاتصالات</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5026</t>
-  </si>
-  <si>
     <t>1093 الرمز البريدي 11732</t>
   </si>
   <si>
@@ -69,9 +63,6 @@
     <t>القويسمة - شارع اليرموك - قرب دوار الشرق الأوسط</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5025</t>
-  </si>
-  <si>
     <t>620823 الرمز البريدي 11162</t>
   </si>
   <si>
@@ -81,9 +72,6 @@
     <t>جبل عمان - شارع البحتري - الدوار الثاني / فوق مطعم أبو جبارة</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5013</t>
-  </si>
-  <si>
     <t>840610 الرمز البريدي 11180 عمان</t>
   </si>
   <si>
@@ -93,9 +81,6 @@
     <t>وسط البلد - شارع الملك حسين - قرب مجمع الفحيص التجاري</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5005</t>
-  </si>
-  <si>
     <t>7987 الرمز البريدي 1118</t>
   </si>
   <si>
@@ -105,9 +90,6 @@
     <t>الهاشمية -شارع الهاشمي - مدخل مجمع سفريات بشرى - سال</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5017</t>
-  </si>
-  <si>
     <t>230693 الرمز البريدي 11123</t>
   </si>
   <si>
@@ -117,9 +99,6 @@
     <t>جبل التّاج - شارع التّاج - قرب مسجد البقاعي شارع الحاووز</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5021</t>
-  </si>
-  <si>
     <t>410676 الرمز البريدي 11141</t>
   </si>
   <si>
@@ -129,9 +108,6 @@
     <t>العبدلي - شارع الملك حسين</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5014</t>
-  </si>
-  <si>
     <t>928430 الرمز البريدي 11190</t>
   </si>
   <si>
@@ -141,9 +117,6 @@
     <t>الشميساني - شارع الثقافة - شارع 11 آب</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5002</t>
-  </si>
-  <si>
     <t>925997 الرمز البريدي 11190</t>
   </si>
   <si>
@@ -153,9 +126,6 @@
     <t>فرع العبدلي مول : محافظة العاصمة - منطقة العبدلي -شارع الاستثمار- مجمع العبدلي مول التجاري الطابق الثاني.</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5008</t>
-  </si>
-  <si>
     <t>927988 الرمز البريدي 11190</t>
   </si>
   <si>
@@ -165,9 +135,6 @@
     <t>ضاحية الياسمين -شارع جبل عرفات - مجمع معتز الكسواني</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5029</t>
-  </si>
-  <si>
     <t>710068 عمان - الأردن 11117</t>
   </si>
   <si>
@@ -177,9 +144,6 @@
     <t>حي نزّال - شارع الدستور - مقابل حلويات العنبتاوي</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5023</t>
-  </si>
-  <si>
     <t>710999 الرمز البريدي 11171</t>
   </si>
   <si>
@@ -189,9 +153,6 @@
     <t>لواء ناعور - مأدبا الغربي - حي الشهيد - مجمع الساكت التجاري 114 الرمز البريدي 11710</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5028</t>
-  </si>
-  <si>
     <t>114 الرمز البريدي 11710</t>
   </si>
   <si>
@@ -201,9 +162,6 @@
     <t>الجيزة - شارع الطريق الصحراوي - قرب مديرية تربية البادية</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5040</t>
-  </si>
-  <si>
     <t>282 الرمز البريدي 16010</t>
   </si>
   <si>
@@ -213,9 +171,6 @@
     <t>أبو علندا - شارع الحزام - مقابل مدينة أبو علندا الصناعية</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5066</t>
-  </si>
-  <si>
     <t>742 الرمز البريدي 11592</t>
   </si>
   <si>
@@ -225,9 +180,6 @@
     <t>خريبة السّوق - شارع الكفاح - مقابل مثلث جمعية المركز الإسلامي الخيرية</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5030</t>
-  </si>
-  <si>
     <t>987 الرمز البريدي 11621 خريبة السوق</t>
   </si>
   <si>
@@ -237,9 +189,6 @@
     <t>المقابلين -شارع الحرية - مقابل محطة توتال للمحروقات</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5031</t>
-  </si>
-  <si>
     <t>606 عمان- الأردن 11623</t>
   </si>
   <si>
@@ -249,9 +198,6 @@
     <t>سحاب/ قرب سوق الخضار 647 الرمز البريدي 11511 شارع الأمير حسن</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5058</t>
-  </si>
-  <si>
     <t>647 الرمز البريدي 11511</t>
   </si>
   <si>
@@ -261,9 +207,6 @@
     <t>صويلح - شارع الاميرة راية</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5053</t>
-  </si>
-  <si>
     <t>717 الرمز البريدي 11910</t>
   </si>
   <si>
@@ -273,10 +216,67 @@
     <t>أبو نصير - شارع العرب - قرب دوار الجامعة التطبيقية</t>
   </si>
   <si>
-    <t>+962 6 5670000 Ext. 5032</t>
-  </si>
-  <si>
     <t>541405 الرمز البريدي 11937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فرعي </t>
+  </si>
+  <si>
+    <t>Ext. 5004</t>
+  </si>
+  <si>
+    <t>Ext. 5026</t>
+  </si>
+  <si>
+    <t>Ext. 5025</t>
+  </si>
+  <si>
+    <t>Ext. 5013</t>
+  </si>
+  <si>
+    <t>Ext. 5005</t>
+  </si>
+  <si>
+    <t>Ext. 5017</t>
+  </si>
+  <si>
+    <t>Ext. 5021</t>
+  </si>
+  <si>
+    <t>Ext. 5014</t>
+  </si>
+  <si>
+    <t>Ext. 5002</t>
+  </si>
+  <si>
+    <t>Ext. 5008</t>
+  </si>
+  <si>
+    <t>Ext. 5029</t>
+  </si>
+  <si>
+    <t>Ext. 5028</t>
+  </si>
+  <si>
+    <t>Ext. 5040</t>
+  </si>
+  <si>
+    <t>Ext. 5066</t>
+  </si>
+  <si>
+    <t>Ext. 5030</t>
+  </si>
+  <si>
+    <t>Ext. 5031</t>
+  </si>
+  <si>
+    <t>Ext. 5058</t>
+  </si>
+  <si>
+    <t>Ext. 5053</t>
+  </si>
+  <si>
+    <t>Ext. 5032</t>
   </si>
 </sst>
 </file>
@@ -338,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -346,9 +346,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="عادي" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -626,307 +635,371 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="71.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="84.28515625" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
+      <c r="C4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="2" t="s">
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
+      <c r="C8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="2" t="s">
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="C9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
+    <row r="10" spans="1:5">
+      <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="2" t="s">
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="2" t="s">
+      <c r="B11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="2" t="s">
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
+      <c r="C12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="2" t="s">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="C13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="30">
-      <c r="A11" s="2" t="s">
+    <row r="14" spans="1:5">
+      <c r="A14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="2" t="s">
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C15" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="2" t="s">
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
+      <c r="C16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="2" t="s">
+    </row>
+    <row r="17" spans="1:5" ht="30">
+      <c r="A17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="C17" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="30">
-      <c r="A14" s="2" t="s">
+    <row r="18" spans="1:5">
+      <c r="A18" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="2" t="s">
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C19" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="2" t="s">
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
+      <c r="C20" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="2" t="s">
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="C21" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="2">
+        <v>65670000</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
